--- a/results/finance/finance_merge_matrix.xlsx
+++ b/results/finance/finance_merge_matrix.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuel.moertl\Privat\BSc\code\uvl_merger\results\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F771D3B9-6908-44B1-9C84-1FDA7C58F8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E8EF7F-CE8E-4936-A246-A71DCE954496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShareRatio_%" sheetId="1" r:id="rId1"/>
-    <sheet name="ContextShare_%" sheetId="2" r:id="rId2"/>
-    <sheet name="Reduction_%" sheetId="3" r:id="rId3"/>
+    <sheet name="Reduction_%" sheetId="3" r:id="rId2"/>
+    <sheet name="ContextShare_%" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -48,14 +48,14 @@
     <t>finance_9</t>
   </si>
   <si>
-    <t>finance_10</t>
+    <t>finance_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +67,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -107,11 +113,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -425,36 +433,36 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>98.88</v>
@@ -483,7 +491,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>98.88</v>
@@ -512,7 +520,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>97.63</v>
@@ -541,7 +549,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>95.32</v>
@@ -570,7 +578,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>57.33</v>
@@ -599,7 +607,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>53.19</v>
@@ -628,7 +636,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>51.44</v>
@@ -657,7 +665,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>50.2</v>
@@ -686,7 +694,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>50.36</v>
@@ -713,9 +721,139 @@
         <v>96.82</v>
       </c>
     </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A10">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:J1">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:J10">
     <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:J21">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -729,6 +867,372 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3">
+        <v>51.01</v>
+      </c>
+      <c r="D2" s="3">
+        <v>49.12</v>
+      </c>
+      <c r="E2" s="3">
+        <v>48.82</v>
+      </c>
+      <c r="F2" s="3">
+        <v>28.42</v>
+      </c>
+      <c r="G2" s="3">
+        <v>27.28</v>
+      </c>
+      <c r="H2" s="3">
+        <v>21.89</v>
+      </c>
+      <c r="I2" s="3">
+        <v>21.63</v>
+      </c>
+      <c r="J2" s="3">
+        <v>21.39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>51.01</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>49.34</v>
+      </c>
+      <c r="E3" s="3">
+        <v>49.04</v>
+      </c>
+      <c r="F3" s="3">
+        <v>28.76</v>
+      </c>
+      <c r="G3" s="3">
+        <v>27.62</v>
+      </c>
+      <c r="H3" s="3">
+        <v>22.19</v>
+      </c>
+      <c r="I3" s="3">
+        <v>21.84</v>
+      </c>
+      <c r="J3" s="3">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3">
+        <v>49.12</v>
+      </c>
+      <c r="C4" s="3">
+        <v>49.34</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
+        <v>50.96</v>
+      </c>
+      <c r="F4" s="3">
+        <v>28.63</v>
+      </c>
+      <c r="G4" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>22.08</v>
+      </c>
+      <c r="I4" s="3">
+        <v>21.73</v>
+      </c>
+      <c r="J4" s="3">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3">
+        <v>48.82</v>
+      </c>
+      <c r="C5" s="3">
+        <v>49.04</v>
+      </c>
+      <c r="D5" s="3">
+        <v>50.96</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>28.72</v>
+      </c>
+      <c r="G5" s="3">
+        <v>27.54</v>
+      </c>
+      <c r="H5" s="3">
+        <v>22.13</v>
+      </c>
+      <c r="I5" s="3">
+        <v>21.78</v>
+      </c>
+      <c r="J5" s="3">
+        <v>21.54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3">
+        <v>28.42</v>
+      </c>
+      <c r="C6" s="3">
+        <v>28.76</v>
+      </c>
+      <c r="D6" s="3">
+        <v>28.63</v>
+      </c>
+      <c r="E6" s="3">
+        <v>28.72</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3">
+        <v>46.07</v>
+      </c>
+      <c r="H6" s="3">
+        <v>36.1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="J6" s="3">
+        <v>35.200000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3">
+        <v>27.28</v>
+      </c>
+      <c r="C7" s="3">
+        <v>27.62</v>
+      </c>
+      <c r="D7" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>27.54</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46.07</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>40.4</v>
+      </c>
+      <c r="I7" s="3">
+        <v>39.75</v>
+      </c>
+      <c r="J7" s="3">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3">
+        <v>21.89</v>
+      </c>
+      <c r="C8" s="3">
+        <v>22.19</v>
+      </c>
+      <c r="D8" s="3">
+        <v>22.08</v>
+      </c>
+      <c r="E8" s="3">
+        <v>22.13</v>
+      </c>
+      <c r="F8" s="3">
+        <v>36.1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>40.4</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
+        <v>50.9</v>
+      </c>
+      <c r="J8" s="3">
+        <v>50.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3">
+        <v>21.63</v>
+      </c>
+      <c r="C9" s="3">
+        <v>21.84</v>
+      </c>
+      <c r="D9" s="3">
+        <v>21.73</v>
+      </c>
+      <c r="E9" s="3">
+        <v>21.78</v>
+      </c>
+      <c r="F9" s="3">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="G9" s="3">
+        <v>39.75</v>
+      </c>
+      <c r="H9" s="3">
+        <v>50.9</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3">
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3">
+        <v>21.39</v>
+      </c>
+      <c r="C10" s="3">
+        <v>21.6</v>
+      </c>
+      <c r="D10" s="3">
+        <v>21.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>21.54</v>
+      </c>
+      <c r="F10" s="3">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="G10" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>50.14</v>
+      </c>
+      <c r="I10" s="3">
+        <v>50.35</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:A10">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:J1">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:J10">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:J10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -740,36 +1244,36 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>1.34</v>
@@ -798,7 +1302,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>1.34</v>
@@ -827,7 +1331,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>1.89</v>
@@ -856,7 +1360,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>2.91</v>
@@ -885,7 +1389,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6">
         <v>13.49</v>
@@ -914,7 +1418,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>15.46</v>
@@ -943,7 +1447,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>22.59</v>
@@ -972,7 +1476,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>22.35</v>
@@ -1001,7 +1505,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>22.73</v>
@@ -1029,8 +1533,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:J10">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1039,318 +1544,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>51.01</v>
-      </c>
-      <c r="D2">
-        <v>49.12</v>
-      </c>
-      <c r="E2">
-        <v>48.82</v>
-      </c>
-      <c r="F2">
-        <v>28.42</v>
-      </c>
-      <c r="G2">
-        <v>27.28</v>
-      </c>
-      <c r="H2">
-        <v>21.89</v>
-      </c>
-      <c r="I2">
-        <v>21.63</v>
-      </c>
-      <c r="J2">
-        <v>21.39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>51.01</v>
-      </c>
-      <c r="D3">
-        <v>49.34</v>
-      </c>
-      <c r="E3">
-        <v>49.04</v>
-      </c>
-      <c r="F3">
-        <v>28.76</v>
-      </c>
-      <c r="G3">
-        <v>27.62</v>
-      </c>
-      <c r="H3">
-        <v>22.19</v>
-      </c>
-      <c r="I3">
-        <v>21.84</v>
-      </c>
-      <c r="J3">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>49.12</v>
-      </c>
-      <c r="C4">
-        <v>49.34</v>
-      </c>
-      <c r="E4">
-        <v>50.96</v>
-      </c>
-      <c r="F4">
-        <v>28.63</v>
-      </c>
-      <c r="G4">
-        <v>27.5</v>
-      </c>
-      <c r="H4">
-        <v>22.08</v>
-      </c>
-      <c r="I4">
-        <v>21.73</v>
-      </c>
-      <c r="J4">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>48.82</v>
-      </c>
-      <c r="C5">
-        <v>49.04</v>
-      </c>
-      <c r="D5">
-        <v>50.96</v>
-      </c>
-      <c r="F5">
-        <v>28.72</v>
-      </c>
-      <c r="G5">
-        <v>27.54</v>
-      </c>
-      <c r="H5">
-        <v>22.13</v>
-      </c>
-      <c r="I5">
-        <v>21.78</v>
-      </c>
-      <c r="J5">
-        <v>21.54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>28.42</v>
-      </c>
-      <c r="C6">
-        <v>28.76</v>
-      </c>
-      <c r="D6">
-        <v>28.63</v>
-      </c>
-      <c r="E6">
-        <v>28.72</v>
-      </c>
-      <c r="G6">
-        <v>46.07</v>
-      </c>
-      <c r="H6">
-        <v>36.1</v>
-      </c>
-      <c r="I6">
-        <v>35.450000000000003</v>
-      </c>
-      <c r="J6">
-        <v>35.200000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>27.28</v>
-      </c>
-      <c r="C7">
-        <v>27.62</v>
-      </c>
-      <c r="D7">
-        <v>27.5</v>
-      </c>
-      <c r="E7">
-        <v>27.54</v>
-      </c>
-      <c r="F7">
-        <v>46.07</v>
-      </c>
-      <c r="H7">
-        <v>40.4</v>
-      </c>
-      <c r="I7">
-        <v>39.75</v>
-      </c>
-      <c r="J7">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>21.89</v>
-      </c>
-      <c r="C8">
-        <v>22.19</v>
-      </c>
-      <c r="D8">
-        <v>22.08</v>
-      </c>
-      <c r="E8">
-        <v>22.13</v>
-      </c>
-      <c r="F8">
-        <v>36.1</v>
-      </c>
-      <c r="G8">
-        <v>40.4</v>
-      </c>
-      <c r="I8">
-        <v>50.9</v>
-      </c>
-      <c r="J8">
-        <v>50.14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>21.63</v>
-      </c>
-      <c r="C9">
-        <v>21.84</v>
-      </c>
-      <c r="D9">
-        <v>21.73</v>
-      </c>
-      <c r="E9">
-        <v>21.78</v>
-      </c>
-      <c r="F9">
-        <v>35.450000000000003</v>
-      </c>
-      <c r="G9">
-        <v>39.75</v>
-      </c>
-      <c r="H9">
-        <v>50.9</v>
-      </c>
-      <c r="J9">
-        <v>50.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>21.39</v>
-      </c>
-      <c r="C10">
-        <v>21.6</v>
-      </c>
-      <c r="D10">
-        <v>21.5</v>
-      </c>
-      <c r="E10">
-        <v>21.54</v>
-      </c>
-      <c r="F10">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="G10">
-        <v>39.5</v>
-      </c>
-      <c r="H10">
-        <v>50.14</v>
-      </c>
-      <c r="I10">
-        <v>50.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A1:J10">
+  <conditionalFormatting sqref="B2:J10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
         <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
